--- a/Excel/EquipXiLianConfig.xlsx
+++ b/Excel/EquipXiLianConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4D34E7-1F1F-4D98-B864-872E93394B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DC01A0-8E51-428A-B89B-777193BB6CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipXiLianProto" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>Id</t>
   </si>
@@ -222,6 +222,49 @@
   </si>
   <si>
     <t>10010083;300@11300008;1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>Junior Alchemist</t>
+  </si>
+  <si>
+    <t>1st-level Refining Master</t>
+  </si>
+  <si>
+    <t>2nd-level Enchanting Master</t>
+  </si>
+  <si>
+    <t>3rd-level Refining Master</t>
+  </si>
+  <si>
+    <t>4th Level Enchanting Master</t>
+  </si>
+  <si>
+    <t>5th-level Refining Master</t>
+  </si>
+  <si>
+    <t>6-level Refining Master</t>
+  </si>
+  <si>
+    <t>7th-level Refining Master</t>
+  </si>
+  <si>
+    <t>8th Level Refining Master</t>
+  </si>
+  <si>
+    <t>9-level Refining Master</t>
+  </si>
+  <si>
+    <t>10th Level Refining Master</t>
+  </si>
+  <si>
+    <t>11th-level Refining Master</t>
+  </si>
+  <si>
+    <t>12th level refining master</t>
+  </si>
+  <si>
+    <t>Title_EN</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -756,20 +799,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1022"/>
+  <dimension ref="A1:M1022"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.125" style="2" customWidth="1"/>
-    <col min="4" max="9" width="15.125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="30.625" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="4" max="10" width="15.125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
@@ -786,16 +829,19 @@
         <v>4</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
@@ -812,16 +858,19 @@
         <v>11</v>
       </c>
       <c r="H4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
@@ -838,16 +887,19 @@
         <v>16</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="8">
@@ -865,17 +917,20 @@
       <c r="G6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="8">
-        <v>0</v>
+      <c r="H6" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="I6" s="8">
         <v>0</v>
       </c>
-      <c r="J6" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="8">
@@ -893,17 +948,20 @@
       <c r="G7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="8">
-        <v>0</v>
+      <c r="H7" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="I7" s="8">
         <v>0</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="8">
@@ -921,17 +979,20 @@
       <c r="G8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="8">
-        <v>0</v>
+      <c r="H8" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="I8" s="8">
         <v>0</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="8">
@@ -949,17 +1010,20 @@
       <c r="G9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="8">
-        <v>0</v>
+      <c r="H9" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="I9" s="8">
         <v>0</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="8">
@@ -977,17 +1041,20 @@
       <c r="G10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="8">
-        <v>0</v>
+      <c r="H10" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="I10" s="8">
         <v>0</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="8">
         <v>100105</v>
       </c>
@@ -1003,18 +1070,21 @@
       <c r="G11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="8">
-        <v>0</v>
+      <c r="H11" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="1"/>
-    </row>
-    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="8">
         <v>100106</v>
       </c>
@@ -1030,18 +1100,21 @@
       <c r="G12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="8">
-        <v>0</v>
+      <c r="H12" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="I12" s="8">
         <v>0</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="8">
         <v>100107</v>
       </c>
@@ -1057,18 +1130,21 @@
       <c r="G13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="8">
-        <v>0</v>
+      <c r="H13" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="I13" s="8">
         <v>0</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="8">
         <v>100108</v>
       </c>
@@ -1084,18 +1160,21 @@
       <c r="G14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="8">
-        <v>0</v>
+      <c r="H14" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="I14" s="8">
         <v>0</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="8">
         <v>100109</v>
       </c>
@@ -1111,18 +1190,21 @@
       <c r="G15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="8">
-        <v>0</v>
+      <c r="H15" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="I15" s="8">
         <v>0</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="8">
         <v>100110</v>
       </c>
@@ -1138,18 +1220,21 @@
       <c r="G16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="8">
-        <v>0</v>
+      <c r="H16" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="I16" s="8">
         <v>0</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+      <c r="K16" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="8">
         <v>100111</v>
       </c>
@@ -1165,17 +1250,20 @@
       <c r="G17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="8">
-        <v>0</v>
+      <c r="H17" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="I17" s="8">
         <v>0</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="8">
         <v>100112</v>
       </c>
@@ -1191,17 +1279,20 @@
       <c r="G18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="8">
-        <v>0</v>
+      <c r="H18" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="I18" s="8">
         <v>0</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+      <c r="K18" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -1209,8 +1300,9 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -1218,8 +1310,9 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1227,8 +1320,9 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -1236,8 +1330,9 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -1245,8 +1340,9 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1254,8 +1350,9 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -1263,8 +1360,9 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1272,8 +1370,9 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -1281,8 +1380,9 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1290,8 +1390,9 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1299,8 +1400,9 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -1308,8 +1410,9 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -1317,8 +1420,9 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -1326,6 +1430,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="34" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1359,7 +1464,7 @@
     <row r="62" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="63" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="64" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -1370,8 +1475,9 @@
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
-    </row>
-    <row r="66" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K65" s="3"/>
+    </row>
+    <row r="66" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -1382,8 +1488,9 @@
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
-    </row>
-    <row r="67" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K66" s="3"/>
+    </row>
+    <row r="67" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -1394,8 +1501,9 @@
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-    </row>
-    <row r="68" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K67" s="3"/>
+    </row>
+    <row r="68" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -1406,19 +1514,20 @@
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
-    </row>
-    <row r="69" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="K68" s="3"/>
+    </row>
+    <row r="69" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="81" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="82" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="83" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -1563,11 +1672,11 @@
     <row r="222" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="223" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="224" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="226" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="227" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="228" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="229" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -1578,8 +1687,9 @@
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
-    </row>
-    <row r="230" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K229" s="2"/>
+    </row>
+    <row r="230" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -1590,8 +1700,9 @@
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
       <c r="J230" s="2"/>
-    </row>
-    <row r="231" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K230" s="2"/>
+    </row>
+    <row r="231" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -1602,8 +1713,9 @@
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
       <c r="J231" s="2"/>
-    </row>
-    <row r="232" spans="1:10" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K231" s="2"/>
+    </row>
+    <row r="232" spans="1:11" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -1614,8 +1726,9 @@
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
       <c r="J232" s="2"/>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K232" s="2"/>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
@@ -1623,8 +1736,9 @@
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
       <c r="J233" s="2"/>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K233" s="2"/>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
@@ -1632,8 +1746,9 @@
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
       <c r="J234" s="2"/>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K234" s="2"/>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
@@ -1641,8 +1756,9 @@
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
       <c r="J235" s="2"/>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K235" s="2"/>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
@@ -1650,8 +1766,9 @@
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K236" s="2"/>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
@@ -1659,8 +1776,9 @@
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
       <c r="J237" s="2"/>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K237" s="2"/>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
@@ -1668,8 +1786,9 @@
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
       <c r="J238" s="2"/>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K238" s="2"/>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
@@ -1677,8 +1796,9 @@
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
       <c r="J239" s="2"/>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K239" s="2"/>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
@@ -1686,6 +1806,7 @@
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
       <c r="J240" s="2"/>
+      <c r="K240" s="2"/>
     </row>
     <row r="241" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="242" s="2" customFormat="1" x14ac:dyDescent="0.3"/>

--- a/Excel/EquipXiLianConfig.xlsx
+++ b/Excel/EquipXiLianConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DC01A0-8E51-428A-B89B-777193BB6CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD79F69-097B-4B6D-A551-61444BE81220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipXiLianProto" sheetId="1" r:id="rId1"/>
@@ -225,46 +225,48 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>Junior Alchemist</t>
-  </si>
-  <si>
-    <t>1st-level Refining Master</t>
-  </si>
-  <si>
-    <t>2nd-level Enchanting Master</t>
-  </si>
-  <si>
-    <t>3rd-level Refining Master</t>
-  </si>
-  <si>
-    <t>4th Level Enchanting Master</t>
-  </si>
-  <si>
-    <t>5th-level Refining Master</t>
-  </si>
-  <si>
-    <t>6-level Refining Master</t>
-  </si>
-  <si>
-    <t>7th-level Refining Master</t>
-  </si>
-  <si>
-    <t>8th Level Refining Master</t>
-  </si>
-  <si>
-    <t>9-level Refining Master</t>
-  </si>
-  <si>
-    <t>10th Level Refining Master</t>
-  </si>
-  <si>
-    <t>11th-level Refining Master</t>
-  </si>
-  <si>
-    <t>12th level refining master</t>
-  </si>
-  <si>
     <t>Title_EN</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>level 1 Master</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>level 2 Master</t>
+  </si>
+  <si>
+    <t>level 3 Master</t>
+  </si>
+  <si>
+    <t>level 4 Master</t>
+  </si>
+  <si>
+    <t>level 5 Master</t>
+  </si>
+  <si>
+    <t>level 6 Master</t>
+  </si>
+  <si>
+    <t>level 7 Master</t>
+  </si>
+  <si>
+    <t>level 8 Master</t>
+  </si>
+  <si>
+    <t>level 9 Master</t>
+  </si>
+  <si>
+    <t>level 10 Master</t>
+  </si>
+  <si>
+    <t>level 11 Master</t>
+  </si>
+  <si>
+    <t>level 12 Master</t>
+  </si>
+  <si>
+    <t>level 0 Master</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -805,7 +807,9 @@
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="11.125" style="2" customWidth="1"/>
-    <col min="4" max="10" width="15.125" style="4" customWidth="1"/>
+    <col min="4" max="7" width="15.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="27.125" style="4" customWidth="1"/>
+    <col min="9" max="10" width="15.125" style="4" customWidth="1"/>
     <col min="11" max="11" width="30.625" style="4" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
@@ -858,7 +862,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>12</v>
@@ -918,7 +922,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I6" s="8">
         <v>0</v>
